--- a/lead_generation_forms/023_e_commerce_cloud_fulfillment_demo_registration_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/023_e_commerce_cloud_fulfillment_demo_registration_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Verification</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Verification</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Date Of Birth Verification</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Time Of Birth</t>
+          <t>Time Of Birth Verification</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address Verification</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Company Verification</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Website Verification</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One Verification</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple Verification</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note Verification</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email_verification</t>
+          <t>email_verification_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Verification 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phone_verification</t>
+          <t>phone_verification_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Verification 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>date_of_birth_verification</t>
+          <t>date_of_birth_verification_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Date Of Birth Verification 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'select_1',_'value':_1}</t>
+          <t>select_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Select 1', 'value': 1}</t>
+          <t>Select 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'select_2',_'value':_2}</t>
+          <t>select_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Select 2', 'value': 2}</t>
+          <t>Select 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'select_3',_'value':_3}</t>
+          <t>select_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Select 3', 'value': 3}</t>
+          <t>Select 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'select_1',_'value':_1}</t>
+          <t>select_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Select 1', 'value': 1}</t>
+          <t>Select 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'select_2',_'value':_2}</t>
+          <t>select_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Select 2', 'value': 2}</t>
+          <t>Select 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'select_3',_'value':_3}</t>
+          <t>select_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Select 3', 'value': 3}</t>
+          <t>Select 3</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'select_1',_'value':_1}</t>
+          <t>select_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Select 1', 'value': 1}</t>
+          <t>Select 1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'select_2',_'value':_2}</t>
+          <t>select_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Select 2', 'value': 2}</t>
+          <t>Select 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'select_3',_'value':_3}</t>
+          <t>select_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Select 3', 'value': 3}</t>
+          <t>Select 3</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'select_1',_'value':_1}</t>
+          <t>select_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Select 1', 'value': 1}</t>
+          <t>Select 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'select_2',_'value':_2}</t>
+          <t>select_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Select 2', 'value': 2}</t>
+          <t>Select 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'select_3',_'value':_3}</t>
+          <t>select_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Select 3', 'value': 3}</t>
+          <t>Select 3</t>
         </is>
       </c>
     </row>
